--- a/中国养老金群体分布分析_2025.xlsx
+++ b/中国养老金群体分布分析_2025.xlsx
@@ -9,6 +9,8 @@
   <sheets>
     <sheet name="养老金总览" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="对比图表" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="发达国家对比" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="同人均GDP国家对比" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +23,7 @@
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -62,6 +64,11 @@
     <font>
       <b val="1"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="6">
@@ -118,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -168,6 +175,19 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -437,6 +457,85 @@
 </chartSpace>
 </file>
 
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>普惠/居民层养老金水平 ÷ 人均GDP（%）</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'同人均GDP国家对比'!B14</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'同人均GDP国家对比'!$A$15:$A$20</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'同人均GDP国家对比'!$B$15:$B$20</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
@@ -500,6 +599,33 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>13</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6480000" cy="3240000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1111,4 +1237,711 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>中国 vs 发达国家公共养老金对比（OECD Pensions at a Glance 2025 口径）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="28" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>国家/地区</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>制度模式</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>公共养老金替代率</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>老年收入Gini(65+)</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>群体间待遇差</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>公平性简评</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>中国</t>
+        </is>
+      </c>
+      <c r="B3" s="19" t="inlineStr">
+        <is>
+          <t>分轨制(机关/企业/居民)</t>
+        </is>
+      </c>
+      <c r="C3" s="19" t="inlineStr">
+        <is>
+          <t>约35-45%(企业),80%+(机关),~10%(居民)</t>
+        </is>
+      </c>
+      <c r="D3" s="19" t="inlineStr">
+        <is>
+          <t>约0.4+(养老金自身曾测0.74)</t>
+        </is>
+      </c>
+      <c r="E3" s="19" t="inlineStr">
+        <is>
+          <t>机关vs居民23倍</t>
+        </is>
+      </c>
+      <c r="F3" s="19" t="inlineStr">
+        <is>
+          <t>制度按身份分层，垫底</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>新西兰</t>
+        </is>
+      </c>
+      <c r="B4" s="20" t="inlineStr">
+        <is>
+          <t>普惠型(全民统一NZ Super)</t>
+        </is>
+      </c>
+      <c r="C4" s="20" t="inlineStr">
+        <is>
+          <t>低收入者约61%+</t>
+        </is>
+      </c>
+      <c r="D4" s="20" t="inlineStr">
+        <is>
+          <t>较低</t>
+        </is>
+      </c>
+      <c r="E4" s="20" t="inlineStr">
+        <is>
+          <t>无(人人同额)</t>
+        </is>
+      </c>
+      <c r="F4" s="20" t="inlineStr">
+        <is>
+          <t>最优：彻底去身份化</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>澳大利亚</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>保底+强制储蓄</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>公共&lt;35%,含Super超60%</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>中等</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>小(仅资产审查差异)</t>
+        </is>
+      </c>
+      <c r="F5" s="20" t="inlineStr">
+        <is>
+          <t>兜底有效，再分配温和</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>日本</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>双层社会保险</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>33-38%</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>中等</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>小(基础年金全民同额)</t>
+        </is>
+      </c>
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>基础层统一，公平性好</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>加拿大</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>双层混合(OAS+CPP)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>约37%</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>中等</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>小</t>
+        </is>
+      </c>
+      <c r="F7" s="20" t="inlineStr">
+        <is>
+          <t>普惠+缴费双层，均衡</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>美国</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>社会保险型</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>37-40%</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>0.419(发达国家中最高之一)</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>小(计发规则统一且累进)</t>
+        </is>
+      </c>
+      <c r="F8" s="20" t="inlineStr">
+        <is>
+          <t>制度公平，断缴者贫困高</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>欧陆(德法等)</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>社会保险型</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>德约50%,法约60-75%</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>法国较低</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>小(职业分割但规则统一)</t>
+        </is>
+      </c>
+      <c r="F9" s="20" t="inlineStr">
+        <is>
+          <t>规则统一，待遇较高</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>南欧(西/葡等)</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>单一公共制度</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>75-80%+</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>较低</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>小</t>
+        </is>
+      </c>
+      <c r="F10" s="20" t="inlineStr">
+        <is>
+          <t>替代率最高</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="21" t="inlineStr">
+        <is>
+          <t>核心结论：发达国家无论何种模式，国内计发规则统一；中国的群体差距源于制度分轨本身，而非收入差异</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A12:F12"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>中国 vs 人均GDP相近国家(±15%及边界国)养老金对比（IMF 2025：中国人均GDP $13,862）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>国家</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>人均GDP($,2025)</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>普惠/居民层月待遇(约$)</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>该待遇÷人均GDP</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>群体间待遇差</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>模式</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>公平性简评</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>阿根廷</t>
+        </is>
+      </c>
+      <c r="B3" s="20" t="n">
+        <v>14898</v>
+      </c>
+      <c r="C3" s="20" t="n">
+        <v>250</v>
+      </c>
+      <c r="D3" s="20" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E3" s="20" t="inlineStr">
+        <is>
+          <t>小(宪法托底最低工资)</t>
+        </is>
+      </c>
+      <c r="F3" s="20" t="inlineStr">
+        <is>
+          <t>高福利缴费+普惠兜底</t>
+        </is>
+      </c>
+      <c r="G3" s="20" t="inlineStr">
+        <is>
+          <t>公平性好</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>哈萨克斯坦</t>
+        </is>
+      </c>
+      <c r="B4" s="20" t="n">
+        <v>14692</v>
+      </c>
+      <c r="C4" s="20" t="n">
+        <v>170</v>
+      </c>
+      <c r="D4" s="20" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="E4" s="20" t="inlineStr">
+        <is>
+          <t>小(基础层统一)</t>
+        </is>
+      </c>
+      <c r="F4" s="20" t="inlineStr">
+        <is>
+          <t>基础养老金+积累制</t>
+        </is>
+      </c>
+      <c r="G4" s="20" t="inlineStr">
+        <is>
+          <t>公平性较好</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>墨西哥</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="n">
+        <v>13889</v>
+      </c>
+      <c r="C5" s="20" t="n">
+        <v>170</v>
+      </c>
+      <c r="D5" s="20" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>基础层统一65岁全民领</t>
+        </is>
+      </c>
+      <c r="F5" s="20" t="inlineStr">
+        <is>
+          <t>缴费制+普惠Pensión Bienestar</t>
+        </is>
+      </c>
+      <c r="G5" s="20" t="inlineStr">
+        <is>
+          <t>普惠层公平</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="22" t="inlineStr">
+        <is>
+          <t>中国</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="n">
+        <v>13862</v>
+      </c>
+      <c r="C6" s="23" t="n">
+        <v>38</v>
+      </c>
+      <c r="D6" s="23" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="E6" s="23" t="inlineStr">
+        <is>
+          <t>机关vs居民23倍</t>
+        </is>
+      </c>
+      <c r="F6" s="23" t="inlineStr">
+        <is>
+          <t>分轨制(机关/企业/居民)</t>
+        </is>
+      </c>
+      <c r="G6" s="23" t="inlineStr">
+        <is>
+          <t>同水平组垫底</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>马来西亚</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="n">
+        <v>13125</v>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>≈0(无月领制)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>制度内公平但无兜底</t>
+        </is>
+      </c>
+      <c r="F7" s="20" t="inlineStr">
+        <is>
+          <t>纯EPF强制储蓄</t>
+        </is>
+      </c>
+      <c r="G7" s="20" t="inlineStr">
+        <is>
+          <t>老年贫困靠救济</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>巴西(-23%)</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="n">
+        <v>10713</v>
+      </c>
+      <c r="C8" s="20" t="n">
+        <v>270</v>
+      </c>
+      <c r="D8" s="20" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>小(农村=最低工资)</t>
+        </is>
+      </c>
+      <c r="F8" s="20" t="inlineStr">
+        <is>
+          <t>缴费+农村特殊制度</t>
+        </is>
+      </c>
+      <c r="G8" s="20" t="inlineStr">
+        <is>
+          <t>农村待遇最优</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>俄罗斯(+27%)</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="n">
+        <v>17547</v>
+      </c>
+      <c r="C9" s="20" t="n">
+        <v>260</v>
+      </c>
+      <c r="D9" s="20" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>小(全国统一)</t>
+        </is>
+      </c>
+      <c r="F9" s="20" t="inlineStr">
+        <is>
+          <t>统一社会保险</t>
+        </is>
+      </c>
+      <c r="G9" s="20" t="inlineStr">
+        <is>
+          <t>公平性较好</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="21" t="inlineStr">
+        <is>
+          <t>关键发现：人均GDP几乎相同的墨西哥(65岁全民领约$170/月)是中国居民层($38/月)的4.5倍；巴西农民领全额最低工资($270/月)是中国农民的7倍</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>普惠/居民层待遇 ÷ 人均GDP（%）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>国家</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>待遇占比(%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>阿根廷</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>哈萨克</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>墨西哥</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>中国</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>巴西</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>俄罗斯</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
 </file>